--- a/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_1/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,17 +471,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +495,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Access Requirement; Availability</t>
+          <t>Responsiveness</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -509,33 +510,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Traefik is a modern reverse proxy and load balancer designed to manage incoming and outgoing HTTP and HTTPS traffic. HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Security Service (Traefik) functions as a reverse proxy and load balancer, managing HTTP and HTTPS request routing. [...] Traefik acts as an intermediary for client requests to backend servers. It redirects incoming requests (from users) to the corresponding internal services. Load Balancer: Distributes traffic between multiple instances of a service, improving availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6879</v>
+        <v>0.7603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -543,12 +543,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Security; Integrity</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Traefik</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,11 +558,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Traefik is a modern reverse proxy and load balancer designed to manage incoming and outgoing HTTP and HTTPS traffic. HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Security Service (Traefik) functions as a reverse proxy and load balancer, managing HTTP and HTTPS request routing. [...] Traefik acts as an intermediary for client requests to backend servers. It redirects incoming requests (from users) to the corresponding internal services. Load Balancer: Distributes traffic between multiple instances of a service, improving availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8248</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="4">
@@ -601,32 +601,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6244</v>
+        <v>0.5889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stylization</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -654,27 +654,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering. [...] Next.js supports both Client-Side Rendering (CSR) and Server-Side Rendering (SSR), allowing the choice of the best strategy according to the application's needs.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7467</v>
+        <v>0.6506999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AD06</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M08_C16</t>
+          <t>*CF_M08_C17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -683,11 +683,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -697,80 +697,80 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that offers additional structure, features, and optimizations that allow building applications faster and without the need to configure tools manually.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7212</v>
+        <v>0.7027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C17</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.7033</v>
+        <v>0.6825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Reuse; Modularity</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -793,80 +793,80 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6878</v>
+        <v>0.7319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reuse; Modularity</t>
+          <t>Simplification (of development)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Prisma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, code reuse, and maintainability, facilitating the management of the application.</t>
+          <t>Data Service (PostgreSQL) provides the relational database for storing application data. [...] Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7333</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Simplification (of development)</t>
+          <t>Depuration</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -894,59 +894,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
+          <t>Data Service (PostgreSQL) provides the relational database for storing application data. [...] Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C23</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Compatibility</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Prisma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Prisma is an ORM tool used to simplify database access and management.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.7723</v>
+        <v>0.7446</v>
       </c>
     </row>
   </sheetData>
